--- a/artfynd/A 34215-2024 artfynd.xlsx
+++ b/artfynd/A 34215-2024 artfynd.xlsx
@@ -10380,7 +10380,7 @@
         <v>129466334</v>
       </c>
       <c r="B95" t="n">
-        <v>91601</v>
+        <v>91607</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>129466328</v>
       </c>
       <c r="B96" t="n">
-        <v>92004</v>
+        <v>92010</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>129466327</v>
       </c>
       <c r="B97" t="n">
-        <v>91964</v>
+        <v>91969</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 34215-2024 artfynd.xlsx
+++ b/artfynd/A 34215-2024 artfynd.xlsx
@@ -10380,7 +10380,7 @@
         <v>129466334</v>
       </c>
       <c r="B95" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>129466328</v>
       </c>
       <c r="B96" t="n">
-        <v>92010</v>
+        <v>92011</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>129466327</v>
       </c>
       <c r="B97" t="n">
-        <v>91969</v>
+        <v>91970</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 34215-2024 artfynd.xlsx
+++ b/artfynd/A 34215-2024 artfynd.xlsx
@@ -10380,7 +10380,7 @@
         <v>129466334</v>
       </c>
       <c r="B95" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>129466328</v>
       </c>
       <c r="B96" t="n">
-        <v>92011</v>
+        <v>92016</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>129466327</v>
       </c>
       <c r="B97" t="n">
-        <v>91970</v>
+        <v>91975</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 34215-2024 artfynd.xlsx
+++ b/artfynd/A 34215-2024 artfynd.xlsx
@@ -10380,7 +10380,7 @@
         <v>129466334</v>
       </c>
       <c r="B95" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>129466328</v>
       </c>
       <c r="B96" t="n">
-        <v>92016</v>
+        <v>92020</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>129466327</v>
       </c>
       <c r="B97" t="n">
-        <v>91975</v>
+        <v>91979</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 34215-2024 artfynd.xlsx
+++ b/artfynd/A 34215-2024 artfynd.xlsx
@@ -10380,7 +10380,7 @@
         <v>129466334</v>
       </c>
       <c r="B95" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>129466328</v>
       </c>
       <c r="B96" t="n">
-        <v>92020</v>
+        <v>92022</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>129466327</v>
       </c>
       <c r="B97" t="n">
-        <v>91979</v>
+        <v>91981</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 34215-2024 artfynd.xlsx
+++ b/artfynd/A 34215-2024 artfynd.xlsx
@@ -10578,7 +10578,7 @@
         <v>129466327</v>
       </c>
       <c r="B97" t="n">
-        <v>91981</v>
+        <v>91984</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 34215-2024 artfynd.xlsx
+++ b/artfynd/A 34215-2024 artfynd.xlsx
@@ -10578,7 +10578,7 @@
         <v>129466327</v>
       </c>
       <c r="B97" t="n">
-        <v>91984</v>
+        <v>91987</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 34215-2024 artfynd.xlsx
+++ b/artfynd/A 34215-2024 artfynd.xlsx
@@ -10578,7 +10578,7 @@
         <v>129466327</v>
       </c>
       <c r="B97" t="n">
-        <v>91987</v>
+        <v>91988</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 34215-2024 artfynd.xlsx
+++ b/artfynd/A 34215-2024 artfynd.xlsx
@@ -10578,7 +10578,7 @@
         <v>129466327</v>
       </c>
       <c r="B97" t="n">
-        <v>91988</v>
+        <v>92005</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 34215-2024 artfynd.xlsx
+++ b/artfynd/A 34215-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY88"/>
+  <dimension ref="A1:AZ88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730191</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730267</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730268</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730270</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730217</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730218</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730208</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129466327</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1553,6 +1598,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129466328</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1650,6 +1700,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730227</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1747,6 +1802,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730228</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1844,6 +1904,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730229</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1941,6 +2006,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730231</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2038,6 +2108,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730232</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2135,6 +2210,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730233</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2232,6 +2312,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730234</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2329,6 +2414,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730235</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2426,6 +2516,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730236</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2523,6 +2618,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730237</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2620,6 +2720,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730238</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2717,6 +2822,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730239</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2814,6 +2924,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730240</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2911,6 +3026,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730241</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3008,6 +3128,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730242</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3105,6 +3230,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730243</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3202,6 +3332,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730244</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3299,6 +3434,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730245</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3396,6 +3536,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730246</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3493,6 +3638,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730247</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3590,6 +3740,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730248</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3687,6 +3842,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730249</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3784,6 +3944,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730250</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3881,6 +4046,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730252</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3978,6 +4148,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730253</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4075,6 +4250,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730254</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4172,6 +4352,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730255</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4269,6 +4454,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730256</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4366,6 +4556,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730258</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4463,6 +4658,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730259</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4560,6 +4760,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730260</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4657,6 +4862,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730261</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4754,6 +4964,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730262</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4851,6 +5066,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730263</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4948,6 +5168,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730264</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5045,6 +5270,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730265</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5142,6 +5372,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730266</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5239,6 +5474,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730271</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5349,6 +5589,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570497</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5446,6 +5691,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730192</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5543,6 +5793,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730193</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5640,6 +5895,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730194</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5737,6 +5997,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730195</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5834,6 +6099,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730196</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5931,6 +6201,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730197</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6028,6 +6303,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730198</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6125,6 +6405,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730199</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6222,6 +6507,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730200</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6319,6 +6609,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730201</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6416,6 +6711,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730202</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6513,6 +6813,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730203</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6623,6 +6928,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125567216</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6733,6 +7043,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125571471</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6830,6 +7145,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730219</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6927,6 +7247,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730211</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7024,6 +7349,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730212</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7121,6 +7451,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730213</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7218,6 +7553,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730185</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7315,6 +7655,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730186</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7412,6 +7757,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730187</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7509,6 +7859,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730188</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7606,6 +7961,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730189</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7703,6 +8063,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730190</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7808,6 +8173,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730209</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7932,6 +8302,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125566732</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8051,6 +8426,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570303</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8170,6 +8550,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570600</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8289,6 +8674,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125571424</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8411,6 +8801,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125572892</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8532,6 +8927,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125572766</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8651,6 +9051,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570185</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8748,6 +9153,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730215</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8859,6 +9269,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125569555</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8982,6 +9397,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125569219</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9079,6 +9499,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730204</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9176,6 +9601,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730205</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9273,6 +9703,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730206</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9370,8 +9805,102 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121730207</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>